--- a/prova_real/trimestre_06/resultado_T6.xlsx
+++ b/prova_real/trimestre_06/resultado_T6.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5.34</v>
+        <v>5.01</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>16.55</v>
+        <v>16.68</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.4811</v>
+        <v>0.3829</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>1504.55</v>
+        <v>1516.36</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>10595.45</v>
+        <v>10607.27</v>
       </c>
     </row>
     <row r="3">
@@ -650,17 +650,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>CMIG3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>59.7</v>
+        <v>56.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>13.11</v>
+        <v>11.18</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.56</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.57</v>
+        <v>0.78</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>20.32</v>
+        <v>6.15</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-6.506</v>
+        <v>-4.6772</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>869.09</v>
+        <v>740</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>9960</v>
+        <v>9830.91</v>
       </c>
     </row>
     <row r="4">
@@ -724,17 +724,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>VIVT3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -746,10 +746,10 @@
         <v>54.8</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4.08</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6.61</v>
+        <v>6.65</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2.88</v>
+        <v>3.21</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>18.1</v>
+        <v>14.38</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-3.2892</v>
+        <v>-11.939</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>600.91</v>
+        <v>604.55</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>9691.82</v>
+        <v>9695.450000000001</v>
       </c>
     </row>
     <row r="5">
@@ -798,17 +798,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TGMA3</t>
+          <t>ITUB3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -820,10 +820,10 @@
         <v>54.8</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>10.69</v>
+        <v>6.35</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>5.28</v>
+        <v>4.53</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -846,22 +846,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1.31</v>
+        <v>2.77</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>4.88</v>
+        <v>12.87</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-0.4379</v>
+        <v>-7.7514</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>480</v>
+        <v>411.82</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>9570.91</v>
+        <v>9502.73</v>
       </c>
     </row>
     <row r="6">
@@ -872,17 +872,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CMIG3</t>
+          <t>TGMA3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -894,10 +894,10 @@
         <v>54.8</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>11.44</v>
+        <v>11.22</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5.23</v>
+        <v>4.14</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -920,22 +920,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.8</v>
+        <v>1.31</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>6.3</v>
+        <v>4.95</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>-6.0786</v>
+        <v>-0.2241</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>475.45</v>
+        <v>376.36</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>9566.360000000001</v>
+        <v>9467.27</v>
       </c>
     </row>
     <row r="7">
@@ -946,17 +946,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CURY3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -968,10 +968,10 @@
         <v>56.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>11.24</v>
+        <v>4.04</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4.83</v>
+        <v>3.37</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -994,22 +994,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4.79</v>
+        <v>2.82</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>28.69</v>
+        <v>17.76</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-8.638400000000001</v>
+        <v>-2.8526</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>439.09</v>
+        <v>306.36</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>9530</v>
+        <v>9397.27</v>
       </c>
     </row>
     <row r="8">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TTEN3</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>56.5</v>
+        <v>58.1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>12.61</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4.32</v>
+        <v>2.86</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1068,22 +1068,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>12.43</v>
+        <v>19.59</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-3.5236</v>
+        <v>-5.232</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>392.73</v>
+        <v>260</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>9483.639999999999</v>
+        <v>9350.91</v>
       </c>
     </row>
     <row r="9">
@@ -1094,17 +1094,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ITUB3</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1116,10 +1116,10 @@
         <v>54.8</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>6.66</v>
+        <v>10.61</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3.87</v>
+        <v>0.9</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1142,22 +1142,22 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2.91</v>
+        <v>4.59</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>13.53</v>
+        <v>27.49</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>-9.5381</v>
+        <v>-7.2498</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>351.82</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>9442.73</v>
+        <v>9172.73</v>
       </c>
     </row>
     <row r="10">
@@ -1173,27 +1173,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>10.62</v>
+        <v>11.19</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.88</v>
+        <v>0.13</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1216,22 +1216,22 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>15.87</v>
+        <v>16.77</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>-1.4818</v>
+        <v>-1.7172</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>80</v>
+        <v>11.82</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>9170.91</v>
+        <v>9102.73</v>
       </c>
     </row>
     <row r="11">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1264,10 +1264,10 @@
         <v>56.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-6.34</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>11.6</v>
+        <v>12.69</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>-2.9589</v>
+        <v>-3.9745</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-576.36</v>
+        <v>-792.73</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>8514.549999999999</v>
+        <v>8298.18</v>
       </c>
     </row>
     <row r="12">
@@ -1321,27 +1321,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>15.4</v>
+        <v>15.69</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>-7.18</v>
+        <v>-12.8</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1364,22 +1364,22 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>11.25</v>
+        <v>10.9</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>-3.6157</v>
+        <v>-2.5182</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>-652.73</v>
+        <v>-1163.64</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>8438.18</v>
+        <v>7927.27</v>
       </c>
     </row>
     <row r="13">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IRBR3</t>
+          <t>TTEN3</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1412,10 +1412,10 @@
         <v>53.2</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>11.7</v>
+        <v>9.43</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>37.04</v>
+        <v>2.82</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>4.51</v>
+        <v>1.55</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>10.46</v>
+        <v>10.6</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>0.352</v>
+        <v>-2.4971</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0</v>
@@ -1457,76 +1457,76 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>T-6</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>VIVT3</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-20</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>T-6</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ONCO3</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Pouco Previsível</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="4" t="n">
         <v>53.2</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="n">
+        <v>-36.13</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>81.81999999999999</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ OBSERVAR</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>-14.1312</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="n">
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>-2.036</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1538,17 +1538,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>AGXY3</t>
+          <t>FHER3</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1560,10 +1560,10 @@
         <v>54.8</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-104.67</v>
+        <v>-11.43</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>60</v>
+        <v>56.07</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="M15" s="4" t="n">
-        <v>5.35</v>
+        <v>2.3</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>58.3</v>
+        <v>38.3</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-10.5391</v>
+        <v>-3.7857</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>0</v>
@@ -1612,17 +1612,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>FHER3</t>
+          <t>AGXY3</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1634,10 +1634,10 @@
         <v>56.5</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-11.84</v>
+        <v>-112.25</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>42.58</v>
+        <v>38.46</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1660,13 +1660,13 @@
         </is>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.22</v>
+        <v>5.8</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>36.71</v>
+        <v>63.49</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.0408</v>
+        <v>-13.6272</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>0</v>
@@ -1686,17 +1686,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SAPR3</t>
+          <t>TOTS3</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1708,10 +1708,10 @@
         <v>56.5</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.62</v>
+        <v>2.24</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>16.64</v>
+        <v>20.16</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -1734,13 +1734,13 @@
         </is>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.23</v>
+        <v>2.46</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.51</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.1148</v>
+        <v>0.0987</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>0</v>
@@ -1760,17 +1760,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>TOTS3</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1782,10 +1782,10 @@
         <v>54.8</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.28</v>
+        <v>1.07</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>16.22</v>
+        <v>12.51</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.26</v>
+        <v>1.53</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>7.77</v>
+        <v>6.38</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.08160000000000001</v>
+        <v>-0.0377</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>0</v>
@@ -1839,12 +1839,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>59.7</v>
+        <v>61.3</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-70.03</v>
+        <v>-74.97</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>11.88</v>
+        <v>9.9</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>33.63</v>
+        <v>38.52</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-15.0061</v>
+        <v>-18.9457</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>0</v>
@@ -1908,17 +1908,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>BBAS3</t>
+          <t>TIMS3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1930,10 +1930,10 @@
         <v>56.5</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.36</v>
+        <v>2.84</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>11.16</v>
+        <v>7.27</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -1956,13 +1956,13 @@
         </is>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>6.58</v>
+        <v>13.36</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.181</v>
+        <v>-4.0185</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>0</v>
@@ -1982,17 +1982,17 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ONCO3</t>
+          <t>BRSR6</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2001,17 +2001,17 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-32.9</v>
+        <v>0.67</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.31</v>
+        <v>0.85</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>56.84</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-6.7257</v>
+        <v>-9.180300000000001</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>0</v>
@@ -2056,17 +2056,17 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>AXIA3</t>
+          <t>ENEV3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -2078,10 +2078,10 @@
         <v>53.2</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.34</v>
+        <v>2.93</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>8.369999999999999</v>
+        <v>2.18</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.42</v>
+        <v>2.42</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>10.8</v>
+        <v>21.67</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-9.6867</v>
+        <v>-16.772</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>0</v>
@@ -2130,17 +2130,17 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CBAV3</t>
+          <t>SANB11</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2152,14 +2152,14 @@
         <v>53.2</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-7.65</v>
+        <v>1.46</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>7.96</v>
+        <v>1.8</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2178,13 +2178,13 @@
         </is>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.11</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>9.84</v>
+        <v>13.89</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.2174</v>
+        <v>-8.8622</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>0</v>
@@ -2204,46 +2204,46 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>TIMS3</t>
+          <t>LEVE3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>56.5</v>
+        <v>53.2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.06</v>
+        <v>-4.02</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.88</v>
+        <v>1.08</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>14.34</v>
+        <v>5.37</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-5.473</v>
+        <v>-7.2542</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>0</v>
@@ -2278,36 +2278,36 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>BRAV3</t>
+          <t>ALUP11</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>56.5</v>
+        <v>53.2</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-42.21</v>
+        <v>0.4</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.16</v>
+        <v>0.31</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2326,13 +2326,13 @@
         </is>
       </c>
       <c r="M25" s="4" t="n">
-        <v>8.67</v>
+        <v>2.26</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>39.54</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-23.3289</v>
+        <v>-13.9121</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>0</v>
@@ -2352,17 +2352,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>SANB11</t>
+          <t>ENGI11</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2374,24 +2374,24 @@
         <v>53.2</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.21</v>
+        <v>-2.05</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2400,13 +2400,13 @@
         </is>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>15.63</v>
+        <v>12.03</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-12.0518</v>
+        <v>-5.7739</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>0</v>
@@ -2426,41 +2426,41 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ENEV3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.6</v>
+        <v>-0.64</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.25</v>
+        <v>-1.02</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.61</v>
+        <v>3.25</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>23.35</v>
+        <v>6.82</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-20.4928</v>
+        <v>-3.066</v>
       </c>
       <c r="P27" s="4" t="n">
         <v>0</v>
@@ -2500,32 +2500,32 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>LEVE3</t>
+          <t>BRAV3</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-3.37</v>
+        <v>-41.49</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.06</v>
+        <v>-2.25</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.59</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.82</v>
+        <v>39.99</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-11.4445</v>
+        <v>-23.7295</v>
       </c>
       <c r="P28" s="4" t="n">
         <v>0</v>
@@ -2574,32 +2574,32 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>SMFT3</t>
+          <t>COCE5</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>53.2</v>
+        <v>58.1</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.89</v>
+        <v>-12.4</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.7</v>
+        <v>-3.33</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.93</v>
+        <v>1</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.31</v>
+        <v>4.47</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.373</v>
+        <v>-3.5301</v>
       </c>
       <c r="P29" s="4" t="n">
         <v>0</v>
@@ -2648,41 +2648,41 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>BRSR6</t>
+          <t>BRAP4</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.68</v>
+        <v>-0.39</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.06</v>
+        <v>-3.74</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -2696,13 +2696,13 @@
         </is>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.11</v>
+        <v>6.04</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-11.5298</v>
+        <v>-1.8101</v>
       </c>
       <c r="P30" s="4" t="n">
         <v>0</v>
@@ -2722,17 +2722,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>CBAV3</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2744,10 +2744,10 @@
         <v>56.5</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.53</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1</v>
+        <v>-4.71</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
@@ -2756,12 +2756,12 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.4</v>
+        <v>0.59</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>7.14</v>
+        <v>10.31</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.4385</v>
+        <v>-0.3535</v>
       </c>
       <c r="P31" s="4" t="n">
         <v>0</v>
@@ -2796,41 +2796,41 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>PCAR3</t>
+          <t>SMFT3</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>53.2</v>
+        <v>56.5</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.68</v>
+        <v>-3.97</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.37</v>
+        <v>-5.82</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.4</v>
+        <v>1.84</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>15.36</v>
+        <v>10.81</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-4.709</v>
+        <v>-5.1458</v>
       </c>
       <c r="P32" s="4" t="n">
         <v>0</v>
@@ -2870,32 +2870,32 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>COCE5</t>
+          <t>USIM3</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>56.5</v>
+        <v>53.2</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-12.25</v>
+        <v>-13.2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.19</v>
+        <v>-6.96</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.95</v>
+        <v>0.39</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.25</v>
+        <v>6.88</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.7699</v>
+        <v>-0.2793</v>
       </c>
       <c r="P33" s="4" t="n">
         <v>0</v>
@@ -2944,17 +2944,17 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>BRAP4</t>
+          <t>SCAR3</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -2966,10 +2966,10 @@
         <v>54.8</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.53</v>
+        <v>-6.39</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.93</v>
+        <v>-7.49</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.5691</v>
+        <v>-2.2072</v>
       </c>
       <c r="P34" s="4" t="n">
         <v>0</v>
@@ -3018,17 +3018,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ENGI11</t>
+          <t>SMTO3</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3040,10 +3040,10 @@
         <v>54.8</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.61</v>
+        <v>-5.88</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-2.17</v>
+        <v>-10.42</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4.15</v>
+        <v>1.35</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>12.97</v>
+        <v>6.01</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-6.541</v>
+        <v>-0.9292</v>
       </c>
       <c r="P35" s="4" t="n">
         <v>0</v>
@@ -3092,32 +3092,32 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>PTBL3</t>
+          <t>UGPA3</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>58.1</v>
+        <v>53.2</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-6.8</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-3.11</v>
+        <v>-10.8</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
@@ -3140,13 +3140,13 @@
         </is>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.48</v>
+        <v>2.52</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>13.24</v>
+        <v>16.77</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>-2.2974</v>
+        <v>-11.6111</v>
       </c>
       <c r="P36" s="4" t="n">
         <v>0</v>
@@ -3166,36 +3166,36 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>KEPL3</t>
+          <t>RAIL3</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>53.2</v>
+        <v>58.1</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>2.83</v>
+        <v>-1.64</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-5.93</v>
+        <v>-11.6</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.62</v>
+        <v>1.88</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>7.22</v>
+        <v>11</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>-4.0093</v>
+        <v>-4.4063</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>0</v>
@@ -3240,32 +3240,32 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>EGIE3</t>
+          <t>INTB3</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>53.2</v>
+        <v>58.1</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.33</v>
+        <v>-10.26</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-6.12</v>
+        <v>-13.2</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
@@ -3288,13 +3288,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>16.06</v>
+        <v>30.84</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-28.9956</v>
+        <v>-13.6301</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>0</v>
@@ -3314,17 +3314,17 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>AERI3</t>
+          <t>AGRO3</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>61.3</v>
+        <v>58.1</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-20.2</v>
+        <v>-0.8</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-6.19</v>
+        <v>-14.72</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>19.07</v>
+        <v>5.78</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-2.8662</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>0</v>
@@ -3388,32 +3388,32 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>JSLG3</t>
+          <t>PNVL3</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-18.91</v>
+        <v>-1.52</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-8.369999999999999</v>
+        <v>-15.73</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.52</v>
+        <v>1.11</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>12.35</v>
+        <v>13.71</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>-1.3868</v>
+        <v>-5.6472</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>0</v>
@@ -3462,17 +3462,17 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>SMTO3</t>
+          <t>PTBL3</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -3481,13 +3481,13 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>56.5</v>
+        <v>61.3</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-5.04</v>
+        <v>-6.05</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-8.710000000000001</v>
+        <v>-18.26</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
@@ -3510,13 +3510,13 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>1.6</v>
+        <v>0.51</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>7.08</v>
+        <v>14.15</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-1.7725</v>
+        <v>-3.0468</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>0</v>
@@ -3536,32 +3536,32 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>RAIL3</t>
+          <t>JSLG3</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-1.38</v>
+        <v>-18.63</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-9.41</v>
+        <v>-18.4</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>1.88</v>
+        <v>0.52</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>10.96</v>
+        <v>12.33</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-3.8037</v>
+        <v>-1.7837</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>0</v>
@@ -3610,32 +3610,32 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>INTB3</t>
+          <t>AURE3</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-7.92</v>
+        <v>-10.3</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>-9.960000000000001</v>
+        <v>-18.69</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
@@ -3658,13 +3658,13 @@
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>4.34</v>
+        <v>1</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>35.31</v>
+        <v>12.14</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>-14.5313</v>
+        <v>-1.4564</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>0</v>
@@ -3684,17 +3684,17 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>SCAR3</t>
+          <t>JALL3</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>56.5</v>
+        <v>67.7</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-5.95</v>
+        <v>-8.33</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-10.37</v>
+        <v>-18.85</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>9.41</v>
+        <v>23.84</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>-2.1662</v>
+        <v>-19.7148</v>
       </c>
       <c r="P44" s="4" t="n">
         <v>0</v>
@@ -3758,32 +3758,32 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>BRKM5</t>
+          <t>AERI3</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>54.8</v>
+        <v>62.9</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-6.07</v>
+        <v>-18.67</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>-10.5</v>
+        <v>-19.93</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>3.28</v>
+        <v>1.25</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>25.56</v>
+        <v>17.9</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>-6.3554</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>0</v>
@@ -3832,32 +3832,32 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>AURE3</t>
+          <t>BRKM5</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-9.49</v>
+        <v>-5.98</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>-10.52</v>
+        <v>-19.96</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
@@ -3880,13 +3880,13 @@
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>1.09</v>
+        <v>3.26</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>13.21</v>
+        <v>25.55</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>-1.5526</v>
+        <v>-6.5527</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>0</v>
@@ -3906,32 +3906,32 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>UGPA3</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>53.2</v>
+        <v>56.5</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-8.06</v>
+        <v>-30.75</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>-10.68</v>
+        <v>-22.55</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>2.65</v>
+        <v>0.39</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>17.57</v>
+        <v>12.68</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>-10.9959</v>
+        <v>-1.0824</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>0</v>
@@ -3980,32 +3980,32 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>AGRO3</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.7</v>
+        <v>-6.41</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-10.98</v>
+        <v>-24.09</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
@@ -4028,13 +4028,13 @@
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>5.22</v>
+        <v>17.55</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>-3.0652</v>
+        <v>-0.8434</v>
       </c>
       <c r="P48" s="4" t="n">
         <v>0</v>
@@ -4054,17 +4054,17 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>JALL3</t>
+          <t>BEEF3</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>59.7</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-7.19</v>
+        <v>-3.52</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>-11.18</v>
+        <v>-24.22</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>1.21</v>
+        <v>0.95</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>25.88</v>
+        <v>20.55</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>-23.7121</v>
+        <v>-2.9131</v>
       </c>
       <c r="P49" s="4" t="n">
         <v>0</v>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>ANIM3</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -4150,10 +4150,10 @@
         <v>54.8</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-27.35</v>
+        <v>-14.55</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-12.04</v>
+        <v>-25.98</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>15.08</v>
+        <v>25.41</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>-2.0129</v>
+        <v>-2.9261</v>
       </c>
       <c r="P50" s="4" t="n">
         <v>0</v>
@@ -4202,17 +4202,17 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>LJQQ3</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>59.7</v>
+        <v>56.5</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-26.61</v>
+        <v>-25.93</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>-12.72</v>
+        <v>-26.27</v>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
@@ -4250,13 +4250,13 @@
         </is>
       </c>
       <c r="M51" s="4" t="n">
-        <v>0.22</v>
+        <v>0.8</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>12.86</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>-0.5145999999999999</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="P51" s="4" t="n">
         <v>0</v>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -4295,13 +4295,13 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>58.1</v>
+        <v>61.3</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-15.78</v>
+        <v>-17.66</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>-14.73</v>
+        <v>-26.56</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>12.5</v>
+        <v>10.85</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.4292</v>
       </c>
       <c r="P52" s="4" t="n">
         <v>0</v>
@@ -4350,32 +4350,32 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>PNVL3</t>
+          <t>RADL3</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>53.2</v>
+        <v>58.1</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>-1.58</v>
+        <v>-0.47</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>-14.88</v>
+        <v>-26.96</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="M53" s="4" t="n">
-        <v>1.06</v>
+        <v>3.94</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>13</v>
+        <v>19.81</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>-4.7624</v>
+        <v>-4.7674</v>
       </c>
       <c r="P53" s="4" t="n">
         <v>0</v>
@@ -4424,17 +4424,17 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>BEEF3</t>
+          <t>DASA3</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>58.1</v>
+        <v>59.7</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-2.43</v>
+        <v>-28.36</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>-18.93</v>
+        <v>-29.17</v>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
@@ -4472,13 +4472,13 @@
         </is>
       </c>
       <c r="M54" s="4" t="n">
-        <v>1.01</v>
+        <v>0.12</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>21.49</v>
+        <v>6.35</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>-3.5442</v>
+        <v>0.2581</v>
       </c>
       <c r="P54" s="4" t="n">
         <v>0</v>
@@ -4503,12 +4503,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -4517,13 +4517,13 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>56.5</v>
+        <v>59.7</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-2.9</v>
+        <v>-4.97</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>-19.21</v>
+        <v>-29.47</v>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="M55" s="4" t="n">
-        <v>20.85</v>
+        <v>19.25</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>58.2</v>
+        <v>54.28</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>-36.0712</v>
+        <v>-39.4902</v>
       </c>
       <c r="P55" s="4" t="n">
         <v>0</v>
@@ -4572,32 +4572,32 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CSNA3</t>
+          <t>LJQQ3</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>54.8</v>
+        <v>62.9</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-6.62</v>
+        <v>-27.66</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>-20.29</v>
+        <v>-29.97</v>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
@@ -4620,13 +4620,13 @@
         </is>
       </c>
       <c r="M56" s="4" t="n">
-        <v>1.4</v>
+        <v>0.21</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>16.43</v>
+        <v>9.33</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>-0.588</v>
+        <v>-0.4697</v>
       </c>
       <c r="P56" s="4" t="n">
         <v>0</v>
@@ -4646,32 +4646,32 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>LWSA3</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>54.8</v>
+        <v>59.7</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-25.41</v>
+        <v>-2.1</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>-21.43</v>
+        <v>-30.23</v>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
@@ -4694,13 +4694,13 @@
         </is>
       </c>
       <c r="M57" s="4" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>12.74</v>
+        <v>25</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>0.1782</v>
+        <v>-7.4618</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
@@ -4725,27 +4725,27 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>53.2</v>
+        <v>56.5</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-11.12</v>
+        <v>-11.68</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>-21.45</v>
+        <v>-32.35</v>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
@@ -4771,10 +4771,10 @@
         <v>5.87</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>20.48</v>
+        <v>20.64</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>-4.3089</v>
+        <v>-5.5344</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>0</v>
@@ -4794,17 +4794,17 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>DASA3</t>
+          <t>RAIZ4</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -4813,13 +4813,13 @@
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>-28.42</v>
+        <v>-1.45</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>-24.35</v>
+        <v>-33.46</v>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
@@ -4842,13 +4842,13 @@
         </is>
       </c>
       <c r="M59" s="4" t="n">
-        <v>0.12</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>6.26</v>
+        <v>40.9</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>0.337</v>
+        <v>-7.3865</v>
       </c>
       <c r="P59" s="4" t="n">
         <v>0</v>
@@ -4868,17 +4868,17 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>RADL3</t>
+          <t>RENT3</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -4887,13 +4887,13 @@
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>56.5</v>
+        <v>58.1</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.1</v>
+        <v>-3.02</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>-24.68</v>
+        <v>-34.04</v>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
@@ -4916,13 +4916,13 @@
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>3.76</v>
+        <v>7.89</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>18.71</v>
+        <v>26.86</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>-4.1497</v>
+        <v>-6.7609</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
@@ -4942,32 +4942,32 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>LWSA3</t>
+          <t>DESK3</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>58.1</v>
+        <v>54.8</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-2.18</v>
+        <v>-1.78</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>-27.78</v>
+        <v>-36.25</v>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="M61" s="4" t="n">
-        <v>0.72</v>
+        <v>3.68</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>23.14</v>
+        <v>36.54</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>-5.7172</v>
+        <v>-9.1548</v>
       </c>
       <c r="P61" s="4" t="n">
         <v>0</v>
@@ -5016,17 +5016,17 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>SIMH3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -5035,13 +5035,13 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>62.9</v>
+        <v>56.5</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-6.73</v>
+        <v>-7.37</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>-28.49</v>
+        <v>-36.65</v>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
@@ -5064,13 +5064,13 @@
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>41.23</v>
+        <v>39.81</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>-5.333</v>
+        <v>-9.9893</v>
       </c>
       <c r="P62" s="4" t="n">
         <v>0</v>
@@ -5090,32 +5090,32 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>RAIZ4</t>
+          <t>SIMH3</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>54.8</v>
+        <v>67.7</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>-0.7</v>
+        <v>-7.35</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>-29.15</v>
+        <v>-39.5</v>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
@@ -5138,13 +5138,13 @@
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>0.82</v>
+        <v>2.95</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>40.78</v>
+        <v>42.06</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>-7.6739</v>
+        <v>-7.7166</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>0</v>
@@ -5164,32 +5164,32 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>HBSA3</t>
+          <t>SEQL3</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>53.2</v>
+        <v>61.3</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-14.25</v>
+        <v>-41.09</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>-29.5</v>
+        <v>-40.21</v>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
@@ -5212,13 +5212,13 @@
         </is>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.16</v>
+        <v>2.17</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>6.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>0.3031</v>
+        <v>0.3603</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>0</v>
@@ -5238,17 +5238,17 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>RENT3</t>
+          <t>HBSA3</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -5257,13 +5257,13 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>-3.78</v>
+        <v>-14.12</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>-29.94</v>
+        <v>-41.54</v>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
@@ -5286,13 +5286,13 @@
         </is>
       </c>
       <c r="M65" s="4" t="n">
-        <v>7.07</v>
+        <v>0.2</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>23.82</v>
+        <v>7.75</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>-3.3597</v>
+        <v>0.1323</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
@@ -5312,32 +5312,32 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>DESK3</t>
+          <t>MOVI3</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>53.2</v>
+        <v>59.7</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.61</v>
+        <v>-3.77</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>-31.66</v>
+        <v>-44.25</v>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
@@ -5360,13 +5360,13 @@
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>3.74</v>
+        <v>1.77</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>36.54</v>
+        <v>50.58</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>-8.379200000000001</v>
+        <v>-7.214</v>
       </c>
       <c r="P66" s="4" t="n">
         <v>0</v>
@@ -5386,32 +5386,32 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>CSAN3</t>
+          <t>ARML3</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-6.66</v>
+        <v>-18.41</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>-32.09</v>
+        <v>-46.59</v>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
@@ -5434,13 +5434,13 @@
         </is>
       </c>
       <c r="M67" s="4" t="n">
-        <v>3.22</v>
+        <v>1.24</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>39.41</v>
+        <v>28.96</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>-8.396599999999999</v>
+        <v>-1.4948</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>0</v>
@@ -5460,17 +5460,17 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>MOVI3</t>
+          <t>CAML3</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -5479,13 +5479,13 @@
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>59.7</v>
+        <v>71</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-4.42</v>
+        <v>-5.52</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>-38.62</v>
+        <v>-49.91</v>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
@@ -5508,13 +5508,13 @@
         </is>
       </c>
       <c r="M68" s="4" t="n">
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>46.68</v>
+        <v>49.32</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>-3.7156</v>
+        <v>-4.9872</v>
       </c>
       <c r="P68" s="4" t="n">
         <v>0</v>
@@ -5523,228 +5523,6 @@
         <v>0</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>T-6</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>SEQL3</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>2025-02-20</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G69" s="4" t="n">
-        <v>-41.97</v>
-      </c>
-      <c r="H69" s="4" t="n">
-        <v>-38.67</v>
-      </c>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M69" s="4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="O69" s="4" t="n">
-        <v>0.4431</v>
-      </c>
-      <c r="P69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>T-6</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>CAML3</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>2025-02-20</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>-4.24</v>
-      </c>
-      <c r="H70" s="4" t="n">
-        <v>-41.82</v>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v>-4.8882</v>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>T-6</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>ARML3</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>2025-02-20</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G71" s="4" t="n">
-        <v>-18.43</v>
-      </c>
-      <c r="H71" s="4" t="n">
-        <v>-44.78</v>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K71" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>26.81</v>
-      </c>
-      <c r="O71" s="4" t="n">
-        <v>-0.7674</v>
-      </c>
-      <c r="P71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5887,12 +5665,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -5901,13 +5679,13 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5.34</v>
+        <v>5.01</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>16.55</v>
+        <v>16.68</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -5930,22 +5708,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.4811</v>
+        <v>0.3829</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>1504.55</v>
+        <v>1516.36</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>10595.45</v>
+        <v>10607.27</v>
       </c>
     </row>
     <row r="3">
@@ -5956,17 +5734,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>CMIG3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -5975,13 +5753,13 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>59.7</v>
+        <v>56.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>13.11</v>
+        <v>11.18</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.56</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -6004,22 +5782,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.57</v>
+        <v>0.78</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>20.32</v>
+        <v>6.15</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-6.506</v>
+        <v>-4.6772</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>869.09</v>
+        <v>740</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>9960</v>
+        <v>9830.91</v>
       </c>
     </row>
     <row r="4">
@@ -6030,17 +5808,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>VIVT3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6052,10 +5830,10 @@
         <v>54.8</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4.08</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6.61</v>
+        <v>6.65</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -6078,22 +5856,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2.88</v>
+        <v>3.21</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>18.1</v>
+        <v>14.38</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-3.2892</v>
+        <v>-11.939</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>600.91</v>
+        <v>604.55</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>9691.82</v>
+        <v>9695.450000000001</v>
       </c>
     </row>
     <row r="5">
@@ -6104,17 +5882,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TGMA3</t>
+          <t>ITUB3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6126,10 +5904,10 @@
         <v>54.8</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>10.69</v>
+        <v>6.35</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>5.28</v>
+        <v>4.53</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -6152,22 +5930,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1.31</v>
+        <v>2.77</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>4.88</v>
+        <v>12.87</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-0.4379</v>
+        <v>-7.7514</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>480</v>
+        <v>411.82</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>9570.91</v>
+        <v>9502.73</v>
       </c>
     </row>
     <row r="6">
@@ -6178,17 +5956,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CMIG3</t>
+          <t>TGMA3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -6200,10 +5978,10 @@
         <v>54.8</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>11.44</v>
+        <v>11.22</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5.23</v>
+        <v>4.14</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -6226,22 +6004,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.8</v>
+        <v>1.31</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>6.3</v>
+        <v>4.95</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>-6.0786</v>
+        <v>-0.2241</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>475.45</v>
+        <v>376.36</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>9566.360000000001</v>
+        <v>9467.27</v>
       </c>
     </row>
     <row r="7">
@@ -6252,17 +6030,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CURY3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6274,10 +6052,10 @@
         <v>56.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>11.24</v>
+        <v>4.04</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4.83</v>
+        <v>3.37</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -6300,22 +6078,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4.79</v>
+        <v>2.82</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>28.69</v>
+        <v>17.76</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-8.638400000000001</v>
+        <v>-2.8526</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>439.09</v>
+        <v>306.36</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>9530</v>
+        <v>9397.27</v>
       </c>
     </row>
     <row r="8">
@@ -6326,17 +6104,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TTEN3</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -6345,13 +6123,13 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>56.5</v>
+        <v>58.1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>12.61</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4.32</v>
+        <v>2.86</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -6374,22 +6152,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>12.43</v>
+        <v>19.59</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-3.5236</v>
+        <v>-5.232</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>392.73</v>
+        <v>260</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>9483.639999999999</v>
+        <v>9350.91</v>
       </c>
     </row>
     <row r="9">
@@ -6400,17 +6178,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ITUB3</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -6422,10 +6200,10 @@
         <v>54.8</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>6.66</v>
+        <v>10.61</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3.87</v>
+        <v>0.9</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -6448,22 +6226,22 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2.91</v>
+        <v>4.59</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>13.53</v>
+        <v>27.49</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>-9.5381</v>
+        <v>-7.2498</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>351.82</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>9442.73</v>
+        <v>9172.73</v>
       </c>
     </row>
     <row r="10">
@@ -6479,27 +6257,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>10.62</v>
+        <v>11.19</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.88</v>
+        <v>0.13</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -6522,22 +6300,22 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>15.87</v>
+        <v>16.77</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>-1.4818</v>
+        <v>-1.7172</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>80</v>
+        <v>11.82</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>9170.91</v>
+        <v>9102.73</v>
       </c>
     </row>
     <row r="11">
@@ -6553,12 +6331,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -6570,10 +6348,10 @@
         <v>56.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-6.34</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -6596,22 +6374,22 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>11.6</v>
+        <v>12.69</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>-2.9589</v>
+        <v>-3.9745</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-576.36</v>
+        <v>-792.73</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>8514.549999999999</v>
+        <v>8298.18</v>
       </c>
     </row>
     <row r="12">
@@ -6627,27 +6405,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>15.4</v>
+        <v>15.69</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>-7.18</v>
+        <v>-12.8</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -6670,22 +6448,22 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>11.25</v>
+        <v>10.9</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>-3.6157</v>
+        <v>-2.5182</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>9090.91</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>-652.73</v>
+        <v>-1163.64</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>8438.18</v>
+        <v>7927.27</v>
       </c>
     </row>
   </sheetData>
